--- a/templates/Batt Pay Sheet.xlsx
+++ b/templates/Batt Pay Sheet.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kray2\Documents\GitHub\InsulPay\spreadsheet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kray2\Documents\GitHub\InsulPay\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B770AAB9-F30B-426F-9FB3-402C83F31959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F757499-044E-46F4-AC13-7FCBCBB0C5AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{69CF575E-9664-407F-9E4B-BF3015150120}"/>
   </bookViews>
@@ -511,7 +511,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="29.5546875" style="3" customWidth="1"/>
@@ -519,14 +519,14 @@
     <col min="3" max="3" width="10.5546875" style="3" customWidth="1"/>
     <col min="4" max="4" width="9.6640625" style="3" customWidth="1"/>
     <col min="5" max="5" width="11.6640625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="9.88671875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="10.33203125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="9.6640625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="10.5546875" style="3" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="3"/>
+    <col min="6" max="9" width="9.88671875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="10.33203125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="9.6640625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="10.5546875" style="3" customWidth="1"/>
+    <col min="13" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -538,8 +538,11 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" s="4"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -549,8 +552,11 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
         <v>1</v>
@@ -567,17 +573,20 @@
       <c r="F3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -588,9 +597,12 @@
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
-      <c r="I4" s="7"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="7"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -600,8 +612,11 @@
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -611,8 +626,11 @@
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -622,8 +640,11 @@
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -633,8 +654,11 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -644,8 +668,11 @@
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -655,8 +682,11 @@
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -666,8 +696,11 @@
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -677,8 +710,11 @@
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -688,8 +724,11 @@
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -699,8 +738,11 @@
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
       <c r="I14" s="4"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -710,8 +752,11 @@
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -721,8 +766,11 @@
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -732,8 +780,11 @@
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -743,8 +794,11 @@
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -754,6 +808,9 @@
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
